--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513091_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513091_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0744</v>
+        <v>1.9294</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7265</v>
+        <v>1.5686</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3479</v>
+        <v>0.3608</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1752</v>
+        <v>0.1576</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7025</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8777</v>
+        <v>0.8688</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7006</v>
+        <v>1.7263</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3571</v>
+        <v>0.3747</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3435</v>
+        <v>1.3517</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5254</v>
+        <v>-1.5687</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0596</v>
+        <v>-1.0859</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0344</v>
+        <v>0.9054</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4598</v>
+        <v>0.2594</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5746</v>
+        <v>0.646</v>
       </c>
       <c r="V2" t="n">
-        <v>0.66</v>
+        <v>0.6639</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0696</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.0556</v>
+        <v>-1.0008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4161</v>
+        <v>-1.0476</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4717</v>
+        <v>0.0468</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.0769</v>
+        <v>-1.0698</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-2.5114</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1459</v>
+        <v>1.4416</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0027</v>
+        <v>0.7592</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3455</v>
+        <v>-0.5762</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6572</v>
+        <v>1.3354</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0741</v>
+        <v>-1.829</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5855</v>
+        <v>-1.9352</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4887</v>
+        <v>0.1062</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4097</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
+        <v>-2.0245</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.0245</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.2592</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.0415</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-1.1902</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0.4097</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.6116</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2383</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.3733</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.1806</v>
-      </c>
       <c r="X3" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.068</v>
+        <v>-1.2044</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0265</v>
+        <v>-1.9535</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0945</v>
+        <v>0.7491</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1806</v>
+        <v>-3.1298</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3842</v>
+        <v>-1.8371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7964</v>
+        <v>-1.2928</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8057</v>
+        <v>-1.7197</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6476</v>
+        <v>-0.4945</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1581</v>
+        <v>-1.2252</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9863</v>
+        <v>-1.4101</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0318</v>
+        <v>-1.3425</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9545</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6388</v>
+        <v>1.2147</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0727</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4339</v>
+        <v>1.2147</v>
       </c>
       <c r="S4" t="n">
-        <v>4.0252</v>
+        <v>0.642</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1576</v>
+        <v>-0.2338</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8675</v>
+        <v>0.8757</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2737</v>
+        <v>0.0688</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1359</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4096</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4084</v>
+        <v>-1.3047</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.367</v>
+        <v>0.2376</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9586</v>
+        <v>-1.5423</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.0953</v>
+        <v>-2.082</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8122</v>
+        <v>-0.9292</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2832</v>
+        <v>-1.1529</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7371</v>
+        <v>-0.9888</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5016</v>
+        <v>-0.3365</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2355</v>
+        <v>-0.6523</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3583</v>
+        <v>-1.0932</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3106</v>
+        <v>-0.5926</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0477</v>
+        <v>-0.5006</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2291</v>
+        <v>0.4049</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2291</v>
+        <v>0.4049</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3882</v>
+        <v>0.3724</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6299</v>
+        <v>0.0362</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0182</v>
+        <v>0.3362</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0696</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0696</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7936</v>
+        <v>-1.3534</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0921</v>
+        <v>-0.8827</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2985</v>
+        <v>-0.4706</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.6623</v>
+        <v>-1.7553</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8899</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.7723</v>
+        <v>-0.9251</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.7417</v>
+        <v>1.0451</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6909999999999999</v>
+        <v>0.5716</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0508</v>
+        <v>0.4735</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9205</v>
+        <v>-2.8003</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.199</v>
+        <v>-1.4017</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7216</v>
+        <v>-1.3987</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0242</v>
+        <v>-3.0368</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8061</v>
+        <v>1.4508</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4933</v>
+        <v>0.6071</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3129</v>
+        <v>0.8437</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0625</v>
+        <v>0.5707</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1806</v>
+        <v>0.5019</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1181</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8146</v>
+        <v>-1.373</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3878</v>
+        <v>0.3714</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4267</v>
+        <v>-1.7444</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8182</v>
+        <v>-1.3136</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8279</v>
+        <v>-0.0003</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9903</v>
+        <v>-1.3134</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9207</v>
+        <v>0.5722</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5385</v>
+        <v>0.5722</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3822</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7389</v>
+        <v>-1.8859</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3664</v>
+        <v>-0.5725</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3725</v>
+        <v>-1.3134</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6388</v>
+        <v>0.2025</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0727</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4339</v>
+        <v>0.2025</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0886</v>
+        <v>0.0393</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2801</v>
+        <v>-0.2008</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8086</v>
+        <v>0.2401</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5538</v>
+        <v>-0.3011</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4841</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0696</v>
+        <v>-0.3011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8187</v>
+        <v>-2.5721</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0282</v>
+        <v>-2.2308</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.847</v>
+        <v>-0.3414</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3074</v>
+        <v>-4.6758</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0055</v>
+        <v>-1.8973</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3019</v>
+        <v>-2.7785</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5522</v>
+        <v>-2.7095</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5522</v>
+        <v>-0.673</v>
       </c>
       <c r="L8" t="n">
+        <v>-2.0365</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.9663</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1.2243</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.742</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>-1.8596</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.5577</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-1.3019</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.2048</v>
-      </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2048</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4257</v>
+        <v>1.0325</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.524</v>
+        <v>0.3008</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0982</v>
+        <v>0.7317</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2905</v>
+        <v>1.0712</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2905</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0224</v>
+        <v>-2.9394</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1743</v>
+        <v>-0.8647</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1518</v>
+        <v>-2.0748</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0747</v>
+        <v>-1.1816</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5306</v>
+        <v>-0.3572</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4559</v>
+        <v>-0.8244</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6839</v>
+        <v>0.8675</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6346000000000001</v>
+        <v>0.7085</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3185</v>
+        <v>0.159</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7586</v>
+        <v>-2.0491</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.896</v>
+        <v>-1.0657</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1374</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0485</v>
+        <v>-3.0368</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0485</v>
+        <v>1.4172</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2329</v>
+        <v>2.1347</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8097</v>
+        <v>1.1469</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0425</v>
+        <v>0.9878</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1806</v>
+        <v>-2.2729</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1577</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1806</v>
+        <v>-2.4306</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6679</v>
+        <v>-4.3291</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7758</v>
+        <v>-3.2887</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.892</v>
+        <v>-1.0404</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6089</v>
+        <v>-4.634</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9738</v>
+        <v>-1.9954</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6351</v>
+        <v>-2.6386</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.07</v>
+        <v>-2.0337</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0058</v>
+        <v>0.0191</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0758</v>
+        <v>-2.0528</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5389</v>
+        <v>-2.6003</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9796</v>
+        <v>-2.0145</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5593</v>
+        <v>-0.5859</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7593</v>
+        <v>1.1043</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0558</v>
+        <v>0.3406</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8151</v>
+        <v>0.7637</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8205</v>
+        <v>0.8202</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6022</v>
+        <v>-0.6209</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0975</v>
+        <v>-5.2084</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6371</v>
+        <v>-4.9499</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4604</v>
+        <v>-0.2585</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0018</v>
+        <v>-3.9832</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2066</v>
+        <v>-1.187</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7953</v>
+        <v>-2.7962</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6716</v>
+        <v>-2.6121</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0759</v>
+        <v>0.1165</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7475</v>
+        <v>-2.7286</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3302</v>
+        <v>-1.3712</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2825</v>
+        <v>-1.3036</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0477</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7485000000000001</v>
+        <v>0.1085</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.917</v>
+        <v>-0.3133</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1685</v>
+        <v>0.4219</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.6723</v>
+        <v>-19.3559</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.2368</v>
+        <v>-13.0403</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.4355</v>
+        <v>-6.3157</v>
       </c>
       <c r="G12" t="n">
-        <v>-23.6509</v>
+        <v>-23.6675</v>
       </c>
       <c r="H12" t="n">
-        <v>-12.2641</v>
+        <v>-12.2562</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.3868</v>
+        <v>-11.4115</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.56</v>
+        <v>-5.0935</v>
       </c>
       <c r="K12" t="n">
-        <v>0.004399999999999904</v>
+        <v>0.2824</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.564500000000001</v>
+        <v>-5.3758</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.0908</v>
+        <v>-18.5741</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.2687</v>
+        <v>-12.5385</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.822300000000001</v>
+        <v>-6.0359</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.0971</v>
+        <v>-4.0489</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.3635</v>
+        <v>-15.184</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2665</v>
+        <v>11.135</v>
       </c>
       <c r="S12" t="n">
-        <v>8.7721</v>
+        <v>9.049099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6927</v>
+        <v>2.1608</v>
       </c>
       <c r="U12" t="n">
-        <v>7.0794</v>
+        <v>6.8883</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883999999999997</v>
       </c>
       <c r="W12" t="n">
-        <v>4.9942</v>
+        <v>5.0762</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.690900000000001</v>
+        <v>-5.764599999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.975099999999999</v>
+        <v>8.331099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0193</v>
+        <v>4.854</v>
       </c>
       <c r="F13" t="n">
-        <v>3.9558</v>
+        <v>3.4771</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5574</v>
+        <v>7.562</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0477</v>
+        <v>1.0289</v>
       </c>
       <c r="I13" t="n">
-        <v>6.5097</v>
+        <v>6.5332</v>
       </c>
       <c r="J13" t="n">
-        <v>6.4632</v>
+        <v>6.5398</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0206</v>
+        <v>1.0463</v>
       </c>
       <c r="L13" t="n">
-        <v>5.4426</v>
+        <v>5.4934</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0942</v>
+        <v>1.0223</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0272</v>
+        <v>-0.0175</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0671</v>
+        <v>1.0397</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4047</v>
+        <v>-0.2672</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6132</v>
+        <v>-0.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0179</v>
+        <v>0.6328</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2369</v>
+        <v>7.0111</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0939</v>
+        <v>4.0512</v>
       </c>
       <c r="F14" t="n">
-        <v>2.143</v>
+        <v>2.9599</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2479</v>
+        <v>4.2574</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7896</v>
+        <v>1.7984</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4583</v>
+        <v>2.459</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6604</v>
+        <v>3.7509</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4314</v>
+        <v>2.4878</v>
       </c>
       <c r="L14" t="n">
-        <v>1.229</v>
+        <v>1.2631</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5875</v>
+        <v>0.5064</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6418</v>
+        <v>-0.6894</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2293</v>
+        <v>1.1959</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R14" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8061</v>
+        <v>-1.0438</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9407</v>
+        <v>-1.1163</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8655</v>
+        <v>0.0725</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0464</v>
+        <v>3.2776</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2795</v>
+        <v>0.4428</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7669</v>
+        <v>2.8348</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6875</v>
+        <v>3.6686</v>
       </c>
       <c r="H15" t="n">
-        <v>0.755</v>
+        <v>0.7325</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9325</v>
+        <v>2.9361</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3601</v>
+        <v>2.3861</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4488</v>
+        <v>0.4544</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9112</v>
+        <v>1.9317</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3274</v>
+        <v>1.2825</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3062</v>
+        <v>0.2782</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0213</v>
+        <v>1.0043</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8088</v>
+        <v>-0.545</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8515</v>
+        <v>-0.7286</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0427</v>
+        <v>0.1836</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2101</v>
+        <v>2.5511</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0949</v>
+        <v>1.8826</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1152</v>
+        <v>0.6685</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1652</v>
+        <v>2.4779</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9155</v>
+        <v>1.5223</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2497</v>
+        <v>0.9556</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3806</v>
+        <v>2.8033</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2226</v>
+        <v>1.6594</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1581</v>
+        <v>1.1439</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2154</v>
+        <v>-0.3254</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.307</v>
+        <v>-0.1371</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0916</v>
+        <v>-0.1883</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4339</v>
+        <v>1.6196</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.6196</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2085</v>
+        <v>-0.7003</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2857</v>
+        <v>-0.9207</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0772</v>
+        <v>0.2204</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1806</v>
+        <v>-0.846</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1806</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8014</v>
+        <v>2.1323</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7018</v>
+        <v>1.8688</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0997</v>
+        <v>0.2635</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4736</v>
+        <v>2.1848</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5274</v>
+        <v>1.9549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9463</v>
+        <v>0.2298</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7497</v>
+        <v>2.4486</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6393</v>
+        <v>2.2896</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1105</v>
+        <v>0.159</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2761</v>
+        <v>-0.2638</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1119</v>
+        <v>-0.3346</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1642</v>
+        <v>0.0708</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6388</v>
+        <v>1.4172</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6388</v>
+        <v>1.4172</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4787</v>
+        <v>-0.2794</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.048</v>
+        <v>-0.5798</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4307</v>
+        <v>0.3004</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8324</v>
+        <v>-1.1902</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8324</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1683</v>
+        <v>2.0593</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4545</v>
+        <v>-0.3605</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2862</v>
+        <v>2.4198</v>
       </c>
       <c r="G18" t="n">
-        <v>1.652</v>
+        <v>0.8531</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5667</v>
+        <v>-0.216</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0853</v>
+        <v>1.069</v>
       </c>
       <c r="J18" t="n">
-        <v>1.913</v>
+        <v>-0.4673</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8734</v>
+        <v>-0.5143</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0395</v>
+        <v>0.047</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2609</v>
+        <v>1.3204</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3068</v>
+        <v>0.2983</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0458</v>
+        <v>1.022</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2025</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0242</v>
+        <v>1.6196</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9176</v>
+        <v>-1.1502</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4585</v>
+        <v>-0.8809</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4592</v>
+        <v>-0.2693</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5903</v>
+        <v>0.9393</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5903</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9116</v>
+        <v>1.6919</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6298</v>
+        <v>1.5918</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5414</v>
+        <v>0.1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.886</v>
+        <v>1.6558</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1872</v>
+        <v>1.5807</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0732</v>
+        <v>0.0752</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4921</v>
+        <v>1.9362</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5211</v>
+        <v>1.8965</v>
       </c>
       <c r="L19" t="n">
-        <v>0.029</v>
+        <v>0.0398</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3781</v>
+        <v>-0.2804</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3339</v>
+        <v>-0.3158</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0442</v>
+        <v>0.0354</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4339</v>
+        <v>1.0123</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6388</v>
+        <v>1.0123</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3468</v>
+        <v>-0.3811</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1135</v>
+        <v>-0.3444</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2334</v>
+        <v>-0.0367</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9385</v>
+        <v>-0.5951</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2421</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1297</v>
+        <v>-0.1017</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0482</v>
+        <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.178</v>
+        <v>-0.1817</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7935</v>
+        <v>1.7966</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8704</v>
+        <v>1.8775</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0769</v>
+        <v>-0.081</v>
       </c>
       <c r="J20" t="n">
-        <v>1.269</v>
+        <v>1.2843</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2295</v>
+        <v>1.2446</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5245</v>
+        <v>0.5122</v>
       </c>
       <c r="N20" t="n">
-        <v>0.641</v>
+        <v>0.633</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1164</v>
+        <v>-0.1207</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1281</v>
+        <v>-0.1007</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1965</v>
+        <v>-0.1921</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0684</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2562</v>
+        <v>-1.7348</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.012</v>
+        <v>-2.4553</v>
       </c>
       <c r="F21" t="n">
-        <v>3.7558</v>
+        <v>0.7206</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4787</v>
+        <v>-1.2892</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3045</v>
+        <v>0.6722</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8258</v>
+        <v>-1.9614</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9042</v>
+        <v>-1.2856</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2215</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1258</v>
+        <v>-1.9968</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3829</v>
+        <v>-0.0036</v>
       </c>
       <c r="N21" t="n">
-        <v>0.083</v>
+        <v>-0.039</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>0.0354</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4582</v>
+        <v>0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.3018</v>
+        <v>-1.0123</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8436</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5188</v>
+        <v>-0.3971</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.048</v>
+        <v>-0.4084</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5292</v>
+        <v>0.0113</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2916</v>
+        <v>-2.0814</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6149</v>
+        <v>-5.6397</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3232</v>
+        <v>3.5583</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2909</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6745</v>
+        <v>1.3046</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9654</v>
+        <v>-0.8041</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3087</v>
+        <v>-0.8223</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7025</v>
+        <v>1.263</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0112</v>
+        <v>-2.0853</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0178</v>
+        <v>1.3228</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.028</v>
+        <v>0.0416</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0458</v>
+        <v>1.2812</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2048</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0242</v>
+        <v>-4.2515</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2291</v>
+        <v>1.8221</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9635</v>
+        <v>-0.4035</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.524</v>
+        <v>-0.8169</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4395</v>
+        <v>0.4134</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4841</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>19.6723</v>
+        <v>23.1365</v>
       </c>
       <c r="E23" t="n">
-        <v>5.4354</v>
+        <v>6.315700000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>14.2368</v>
+        <v>16.8208</v>
       </c>
       <c r="G23" t="n">
-        <v>23.6509</v>
+        <v>23.66749999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>12.2641</v>
+        <v>12.256</v>
       </c>
       <c r="I23" t="n">
-        <v>11.3869</v>
+        <v>11.4114</v>
       </c>
       <c r="J23" t="n">
-        <v>18.091</v>
+        <v>18.574</v>
       </c>
       <c r="K23" t="n">
-        <v>12.2685</v>
+        <v>12.5385</v>
       </c>
       <c r="L23" t="n">
-        <v>5.8224</v>
+        <v>6.035600000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>5.56</v>
+        <v>5.093399999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.004199999999999916</v>
+        <v>-0.2823</v>
       </c>
       <c r="O23" t="n">
-        <v>5.5645</v>
+        <v>5.3757</v>
       </c>
       <c r="P23" t="n">
-        <v>4.0968</v>
+        <v>4.049199999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-11.2665</v>
+        <v>-11.135</v>
       </c>
       <c r="R23" t="n">
-        <v>15.3635</v>
+        <v>15.184</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.7722</v>
+        <v>-5.2683</v>
       </c>
       <c r="T23" t="n">
-        <v>-7.0796</v>
+        <v>-6.888100000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6929</v>
+        <v>1.6197</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6964000000000001</v>
+        <v>0.6883999999999997</v>
       </c>
       <c r="W23" t="n">
-        <v>5.690799999999999</v>
+        <v>5.764399999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.9943</v>
+        <v>-5.076099999999999</v>
       </c>
     </row>
   </sheetData>
